--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67937E41-13FD-5645-BB73-C58DC456B0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CA86EC-9D19-7C44-9B78-E990FE33F77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3740" yWindow="1740" windowWidth="53300" windowHeight="29520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="920">
   <si>
     <t>Description</t>
   </si>
@@ -2716,6 +2716,90 @@
   </si>
   <si>
     <t>The amount specimen shrinkage, reported as a percentage of total volume</t>
+  </si>
+  <si>
+    <t>d84</t>
+  </si>
+  <si>
+    <t>Grain diameter corresponding to 84 percent passing.  Intermediate value used to report other results.</t>
+  </si>
+  <si>
+    <t>d90</t>
+  </si>
+  <si>
+    <t>Grain diameter corresponding to 90 percent passing.  Intermediate value used to report other results.</t>
+  </si>
+  <si>
+    <t>percent_coarse_gravel</t>
+  </si>
+  <si>
+    <t>percent coarse gravel</t>
+  </si>
+  <si>
+    <t>The percentage of particles that pass the 75 mm sieve and are retained on the 19mm sieve (&lt;75 mm and &gt;19mm).</t>
+  </si>
+  <si>
+    <t>percent_fine_gravel</t>
+  </si>
+  <si>
+    <t>percent fine gravel</t>
+  </si>
+  <si>
+    <t>The percentage of particles that pass the 19 mm sieve and are retained on the 4.75mm sieve (&lt;19 mm and &gt;4.75mm).</t>
+  </si>
+  <si>
+    <t>percent_coarse_sand</t>
+  </si>
+  <si>
+    <t>percent coarse sand</t>
+  </si>
+  <si>
+    <t>The percentage of particles thatpass the #4 sieve and are retained on the #10 sieve (&lt;4.75 mm and &gt;2 mm).</t>
+  </si>
+  <si>
+    <t>percent_medium_sand</t>
+  </si>
+  <si>
+    <t>percent medium sand</t>
+  </si>
+  <si>
+    <t>The percentage of particles thatpass the #10 sieve and are retained on the #40 sieve (&lt;2 mm and &gt;0.425 mm).</t>
+  </si>
+  <si>
+    <t>percent_fine_sand</t>
+  </si>
+  <si>
+    <t>percent fine sand</t>
+  </si>
+  <si>
+    <t>The percentage of particles thatpass the #40 sieve and are retained on the #200 sieve (&lt;0.425 mm and &gt;0.075 mm).</t>
+  </si>
+  <si>
+    <t>aashto_percent_gravel</t>
+  </si>
+  <si>
+    <t>percent gravel aashto</t>
+  </si>
+  <si>
+    <t>The percentage of particles that pass the 75mm sieve and are retained on the #10 sieve (&lt;75 mm and &gt;0.075 mm).</t>
+  </si>
+  <si>
+    <t>aashto_percent_coarse_sand</t>
+  </si>
+  <si>
+    <t>percent coarse sand aashto</t>
+  </si>
+  <si>
+    <t>The percentage of particles that pass the #10 sieve and are retained on the #40 sieve (&lt;2 mm and &gt;0.425 mm).</t>
+  </si>
+  <si>
+    <t>aashto_percent_fine_sand</t>
+  </si>
+  <si>
+    <t>percent fine sand aashto</t>
+  </si>
+  <si>
+    <t>The percentage of particles that pass the #40 sieve and are retained on the #200 sieve (&lt;0.425 mm and &gt;0.075 mm).</t>
   </si>
 </sst>
 </file>
@@ -2981,7 +3065,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3077,6 +3161,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -3304,8 +3398,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:J189" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:J189" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:J199" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:J199" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H180">
     <sortCondition ref="B1:B180"/>
   </sortState>
@@ -3328,8 +3422,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D294" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D294" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D314" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D314" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D294">
     <sortCondition ref="B1:B294"/>
   </sortState>
@@ -3687,7 +3781,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
@@ -7686,6 +7780,216 @@
         <v>1</v>
       </c>
       <c r="F189" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="34">
+      <c r="A190" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B190,AssociatedElements!B$2:B847,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="D190" s="40" t="s">
+        <v>893</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F190" s="41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="34">
+      <c r="A191" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B191,AssociatedElements!B$2:B848,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="D191" s="40" t="s">
+        <v>895</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F191" s="41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="34">
+      <c r="A192" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B192,AssociatedElements!B$2:B849,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="D192" s="40" t="s">
+        <v>898</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F192" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="34">
+      <c r="A193" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B193,AssociatedElements!B$2:B850,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="D193" s="40" t="s">
+        <v>901</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F193" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="34">
+      <c r="A194" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B194,AssociatedElements!B$2:B851,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="D194" s="40" t="s">
+        <v>904</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F194" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="34">
+      <c r="A195" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B195,AssociatedElements!B$2:B852,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="D195" s="40" t="s">
+        <v>907</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F195" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="34">
+      <c r="A196" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B196,AssociatedElements!B$2:B853,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D196" s="40" t="s">
+        <v>910</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F196" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="34">
+      <c r="A197" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B197,AssociatedElements!B$2:B854,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="D197" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F197" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="34">
+      <c r="A198" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B198,AssociatedElements!B$2:B855,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="D198" s="40" t="s">
+        <v>916</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F198" s="41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="34">
+      <c r="A199" s="39" t="str">
+        <f>IF(ISNA(VLOOKUP(B199,AssociatedElements!B$2:B856,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="D199" s="40" t="s">
+        <v>919</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F199" s="41" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7720,7 +8024,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -12132,6 +12436,306 @@
       </c>
       <c r="D294" s="21" t="s">
         <v>884</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="17">
+      <c r="A295" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B295,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B295" s="41" t="s">
+        <v>892</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D295" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="17">
+      <c r="A296" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B296,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B296" s="41" t="s">
+        <v>892</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D296" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="17">
+      <c r="A297" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B297,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B297" s="41" t="s">
+        <v>894</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D297" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="17">
+      <c r="A298" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B298,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B298" s="41" t="s">
+        <v>894</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D298" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="17">
+      <c r="A299" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B299,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B299" s="41" t="s">
+        <v>896</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D299" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="17">
+      <c r="A300" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B300,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B300" s="41" t="s">
+        <v>896</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D300" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="17">
+      <c r="A301" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B301,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B301" s="41" t="s">
+        <v>899</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D301" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="17">
+      <c r="A302" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B302,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B302" s="41" t="s">
+        <v>899</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D302" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="17">
+      <c r="A303" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B303,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B303" s="41" t="s">
+        <v>902</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D303" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="17">
+      <c r="A304" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B304,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B304" s="41" t="s">
+        <v>902</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D304" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="17">
+      <c r="A305" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B305,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B305" s="41" t="s">
+        <v>905</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D305" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="17">
+      <c r="A306" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B306,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B306" s="41" t="s">
+        <v>905</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D306" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="17">
+      <c r="A307" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B307,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B307" s="41" t="s">
+        <v>908</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D307" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="17">
+      <c r="A308" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B308,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B308" s="41" t="s">
+        <v>908</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D308" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="17">
+      <c r="A309" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B309,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B309" s="41" t="s">
+        <v>911</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D309" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="17">
+      <c r="A310" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B310,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B310" s="41" t="s">
+        <v>911</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D310" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="17">
+      <c r="A311" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B311,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B311" s="41" t="s">
+        <v>914</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D311" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="17">
+      <c r="A312" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B312,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B312" s="41" t="s">
+        <v>914</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D312" s="21" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="17">
+      <c r="A313" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B313,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B313" s="41" t="s">
+        <v>917</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D313" s="21" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="17">
+      <c r="A314" s="42" t="str">
+        <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B314,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B314" s="41" t="s">
+        <v>917</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D314" s="21" t="s">
+        <v>768</v>
       </c>
     </row>
   </sheetData>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CA86EC-9D19-7C44-9B78-E990FE33F77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B2F44E-23C8-2141-9CB5-BDB76AF1154E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10020" yWindow="2560" windowWidth="35840" windowHeight="20700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -3065,7 +3065,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3161,16 +3161,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -3270,6 +3260,38 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -3325,38 +3347,6 @@
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -3384,38 +3374,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:J199" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:J199" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:J199" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H180">
     <sortCondition ref="B1:B180"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="20">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B659,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{514A6BB8-33C8-4E31-A303-203B88580677}" name="SLD Comment" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{941837FD-9A64-45F5-AA1B-805F9901FDC7}" name="SLD Changed" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{514A6BB8-33C8-4E31-A303-203B88580677}" name="SLD Comment" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{941837FD-9A64-45F5-AA1B-805F9901FDC7}" name="SLD Changed" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7784,7 +7774,7 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="34">
-      <c r="A190" s="39" t="str">
+      <c r="A190" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B190,AssociatedElements!B$2:B847,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7794,18 +7784,18 @@
       <c r="C190" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="D190" s="40" t="s">
+      <c r="D190" s="2" t="s">
         <v>893</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F190" s="41" t="s">
+      <c r="F190" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="34">
-      <c r="A191" s="39" t="str">
+      <c r="A191" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B191,AssociatedElements!B$2:B848,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7815,18 +7805,18 @@
       <c r="C191" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="D191" s="40" t="s">
+      <c r="D191" s="2" t="s">
         <v>895</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F191" s="41" t="s">
+      <c r="F191" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="34">
-      <c r="A192" s="39" t="str">
+      <c r="A192" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B192,AssociatedElements!B$2:B849,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7836,18 +7826,18 @@
       <c r="C192" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="D192" s="40" t="s">
+      <c r="D192" s="2" t="s">
         <v>898</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F192" s="41" t="s">
+      <c r="F192" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="34">
-      <c r="A193" s="39" t="str">
+      <c r="A193" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B193,AssociatedElements!B$2:B850,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7857,18 +7847,18 @@
       <c r="C193" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="D193" s="40" t="s">
+      <c r="D193" s="2" t="s">
         <v>901</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F193" s="41" t="s">
+      <c r="F193" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="34">
-      <c r="A194" s="39" t="str">
+      <c r="A194" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B194,AssociatedElements!B$2:B851,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7878,18 +7868,18 @@
       <c r="C194" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="D194" s="40" t="s">
+      <c r="D194" s="2" t="s">
         <v>904</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F194" s="41" t="s">
+      <c r="F194" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="34">
-      <c r="A195" s="39" t="str">
+      <c r="A195" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B195,AssociatedElements!B$2:B852,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7899,18 +7889,18 @@
       <c r="C195" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="D195" s="40" t="s">
+      <c r="D195" s="2" t="s">
         <v>907</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F195" s="41" t="s">
+      <c r="F195" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="34">
-      <c r="A196" s="39" t="str">
+      <c r="A196" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B196,AssociatedElements!B$2:B853,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7920,18 +7910,18 @@
       <c r="C196" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="D196" s="40" t="s">
+      <c r="D196" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F196" s="41" t="s">
+      <c r="F196" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="34">
-      <c r="A197" s="39" t="str">
+      <c r="A197" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B197,AssociatedElements!B$2:B854,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7941,18 +7931,18 @@
       <c r="C197" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="D197" s="40" t="s">
+      <c r="D197" s="2" t="s">
         <v>913</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F197" s="41" t="s">
+      <c r="F197" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="34">
-      <c r="A198" s="39" t="str">
+      <c r="A198" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B198,AssociatedElements!B$2:B855,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7962,18 +7952,18 @@
       <c r="C198" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="D198" s="40" t="s">
+      <c r="D198" s="2" t="s">
         <v>916</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F198" s="41" t="s">
+      <c r="F198" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="34">
-      <c r="A199" s="39" t="str">
+      <c r="A199" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B199,AssociatedElements!B$2:B856,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -7983,13 +7973,13 @@
       <c r="C199" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="D199" s="40" t="s">
+      <c r="D199" s="2" t="s">
         <v>919</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F199" s="41" t="s">
+      <c r="F199" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -12439,11 +12429,11 @@
       </c>
     </row>
     <row r="295" spans="1:4" ht="17">
-      <c r="A295" s="42" t="str">
+      <c r="A295" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B295,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B295" s="41" t="s">
+      <c r="B295" s="2" t="s">
         <v>892</v>
       </c>
       <c r="C295" s="4" t="s">
@@ -12454,11 +12444,11 @@
       </c>
     </row>
     <row r="296" spans="1:4" ht="17">
-      <c r="A296" s="42" t="str">
+      <c r="A296" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B296,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B296" s="41" t="s">
+      <c r="B296" s="2" t="s">
         <v>892</v>
       </c>
       <c r="C296" s="4" t="s">
@@ -12469,11 +12459,11 @@
       </c>
     </row>
     <row r="297" spans="1:4" ht="17">
-      <c r="A297" s="42" t="str">
+      <c r="A297" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B297,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B297" s="41" t="s">
+      <c r="B297" s="2" t="s">
         <v>894</v>
       </c>
       <c r="C297" s="4" t="s">
@@ -12484,11 +12474,11 @@
       </c>
     </row>
     <row r="298" spans="1:4" ht="17">
-      <c r="A298" s="42" t="str">
+      <c r="A298" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B298,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B298" s="41" t="s">
+      <c r="B298" s="2" t="s">
         <v>894</v>
       </c>
       <c r="C298" s="4" t="s">
@@ -12499,11 +12489,11 @@
       </c>
     </row>
     <row r="299" spans="1:4" ht="17">
-      <c r="A299" s="42" t="str">
+      <c r="A299" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B299,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B299" s="41" t="s">
+      <c r="B299" s="2" t="s">
         <v>896</v>
       </c>
       <c r="C299" s="4" t="s">
@@ -12514,11 +12504,11 @@
       </c>
     </row>
     <row r="300" spans="1:4" ht="17">
-      <c r="A300" s="42" t="str">
+      <c r="A300" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B300,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B300" s="41" t="s">
+      <c r="B300" s="2" t="s">
         <v>896</v>
       </c>
       <c r="C300" s="4" t="s">
@@ -12529,11 +12519,11 @@
       </c>
     </row>
     <row r="301" spans="1:4" ht="17">
-      <c r="A301" s="42" t="str">
+      <c r="A301" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B301,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B301" s="41" t="s">
+      <c r="B301" s="2" t="s">
         <v>899</v>
       </c>
       <c r="C301" s="4" t="s">
@@ -12544,11 +12534,11 @@
       </c>
     </row>
     <row r="302" spans="1:4" ht="17">
-      <c r="A302" s="42" t="str">
+      <c r="A302" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B302,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B302" s="41" t="s">
+      <c r="B302" s="2" t="s">
         <v>899</v>
       </c>
       <c r="C302" s="4" t="s">
@@ -12559,11 +12549,11 @@
       </c>
     </row>
     <row r="303" spans="1:4" ht="17">
-      <c r="A303" s="42" t="str">
+      <c r="A303" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B303,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B303" s="41" t="s">
+      <c r="B303" s="2" t="s">
         <v>902</v>
       </c>
       <c r="C303" s="4" t="s">
@@ -12574,11 +12564,11 @@
       </c>
     </row>
     <row r="304" spans="1:4" ht="17">
-      <c r="A304" s="42" t="str">
+      <c r="A304" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B304,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B304" s="41" t="s">
+      <c r="B304" s="2" t="s">
         <v>902</v>
       </c>
       <c r="C304" s="4" t="s">
@@ -12589,11 +12579,11 @@
       </c>
     </row>
     <row r="305" spans="1:4" ht="17">
-      <c r="A305" s="42" t="str">
+      <c r="A305" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B305,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B305" s="41" t="s">
+      <c r="B305" s="2" t="s">
         <v>905</v>
       </c>
       <c r="C305" s="4" t="s">
@@ -12604,11 +12594,11 @@
       </c>
     </row>
     <row r="306" spans="1:4" ht="17">
-      <c r="A306" s="42" t="str">
+      <c r="A306" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B306,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B306" s="41" t="s">
+      <c r="B306" s="2" t="s">
         <v>905</v>
       </c>
       <c r="C306" s="4" t="s">
@@ -12619,11 +12609,11 @@
       </c>
     </row>
     <row r="307" spans="1:4" ht="17">
-      <c r="A307" s="42" t="str">
+      <c r="A307" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B307,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B307" s="41" t="s">
+      <c r="B307" s="2" t="s">
         <v>908</v>
       </c>
       <c r="C307" s="4" t="s">
@@ -12634,11 +12624,11 @@
       </c>
     </row>
     <row r="308" spans="1:4" ht="17">
-      <c r="A308" s="42" t="str">
+      <c r="A308" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B308,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B308" s="41" t="s">
+      <c r="B308" s="2" t="s">
         <v>908</v>
       </c>
       <c r="C308" s="4" t="s">
@@ -12649,11 +12639,11 @@
       </c>
     </row>
     <row r="309" spans="1:4" ht="17">
-      <c r="A309" s="42" t="str">
+      <c r="A309" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B309,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B309" s="41" t="s">
+      <c r="B309" s="2" t="s">
         <v>911</v>
       </c>
       <c r="C309" s="4" t="s">
@@ -12664,11 +12654,11 @@
       </c>
     </row>
     <row r="310" spans="1:4" ht="17">
-      <c r="A310" s="42" t="str">
+      <c r="A310" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B310,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B310" s="41" t="s">
+      <c r="B310" s="2" t="s">
         <v>911</v>
       </c>
       <c r="C310" s="4" t="s">
@@ -12679,11 +12669,11 @@
       </c>
     </row>
     <row r="311" spans="1:4" ht="17">
-      <c r="A311" s="42" t="str">
+      <c r="A311" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B311,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B311" s="41" t="s">
+      <c r="B311" s="2" t="s">
         <v>914</v>
       </c>
       <c r="C311" s="4" t="s">
@@ -12694,11 +12684,11 @@
       </c>
     </row>
     <row r="312" spans="1:4" ht="17">
-      <c r="A312" s="42" t="str">
+      <c r="A312" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B312,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B312" s="41" t="s">
+      <c r="B312" s="2" t="s">
         <v>914</v>
       </c>
       <c r="C312" s="4" t="s">
@@ -12709,11 +12699,11 @@
       </c>
     </row>
     <row r="313" spans="1:4" ht="17">
-      <c r="A313" s="42" t="str">
+      <c r="A313" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B313,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B313" s="41" t="s">
+      <c r="B313" s="2" t="s">
         <v>917</v>
       </c>
       <c r="C313" s="4" t="s">
@@ -12724,11 +12714,11 @@
       </c>
     </row>
     <row r="314" spans="1:4" ht="17">
-      <c r="A314" s="42" t="str">
+      <c r="A314" t="str">
         <f>IF(ISNA(VLOOKUP([1]AssociatedElements!B314,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B314" s="41" t="s">
+      <c r="B314" s="2" t="s">
         <v>917</v>
       </c>
       <c r="C314" s="4" t="s">

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -7370,6 +7370,37 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206">
+        <f>IF(ISNA(VLOOKUP(B206,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>critical_creep_load</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Critical Creep Load</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>The load at which the rate of settlement under sustained load becomes unacceptably large - conventionally the load level above which the rate of creep settlement increases sharply with each load increment, taken from a static load test loading schedule that includes sustained-load (creep) readings at one or more increments. A result of diggs:StaticLoadTest.</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7385,7 +7416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D324"/>
+  <dimension ref="A1:D325"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -14160,6 +14191,27 @@
       <c r="D324" s="21" t="inlineStr">
         <is>
           <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <f>IF(ISNA(VLOOKUP(B325,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>critical_creep_load</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:StaticLoadTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -7401,6 +7401,99 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207">
+        <f>IF(ISNA(VLOOKUP(B207,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>modulus_of_subgrade_reaction</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Modulus of Subgrade Reaction</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>The ratio of applied bearing pressure to plate settlement (k) derived from a plate-bearing load test - ASTM D1195/D1196's characteristic output. Force per unit volume (pressure/deflection), reported in units such as kN/m3 or pci.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>force per volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <f>IF(ISNA(VLOOKUP(B208,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>deformation_modulus_first_load</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Deformation Modulus, First Load (Ev1)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>The deformation modulus derived from the load-settlement curve of the FIRST loading cycle of a two-cycle plate-bearing load test, per DIN 18134. Reflects the initial condition of the ground or platform material, including particle rearrangement and closure of air voids.</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <f>IF(ISNA(VLOOKUP(B209,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>deformation_modulus_second_load</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Deformation Modulus, Second Load (Ev2)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>The deformation modulus derived from the load-settlement curve of the SECOND loading cycle of a two-cycle plate-bearing load test, per DIN 18134. Primarily reflects the repeatable elastic behaviour of the ground or platform material after the first cycle's initial compression. The ratio Ev2/Ev1 (see #deformation_modulus_first_load) is DIN 18134's own reported indicator of the degree of compaction achieved.</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7416,7 +7509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D331"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -14212,6 +14305,132 @@
       <c r="D325" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:StaticLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <f>IF(ISNA(VLOOKUP(B326,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>modulus_of_subgrade_reaction</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:PlateLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <f>IF(ISNA(VLOOKUP(B327,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>modulus_of_subgrade_reaction</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ZoneLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <f>IF(ISNA(VLOOKUP(B328,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>deformation_modulus_first_load</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:PlateLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <f>IF(ISNA(VLOOKUP(B329,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>deformation_modulus_first_load</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ZoneLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <f>IF(ISNA(VLOOKUP(B330,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>deformation_modulus_second_load</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:PlateLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <f>IF(ISNA(VLOOKUP(B331,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>deformation_modulus_second_load</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ZoneLoadTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J209"/>
+  <dimension ref="A1:J210"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -7494,6 +7494,37 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210">
+        <f>IF(ISNA(VLOOKUP(B210,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>defect_depth</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Defect Depth</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>The depth from the pile/element head to an interpreted discontinuity, void, necking, or other change in cross-section identified from a low-strain integrity test record. Absent where the test found no defect and the reflection at the recorded travel time is interpreted as the pile toe instead. A result of diggs:LowStrainIntegrityTest.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7509,7 +7540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D331"/>
+  <dimension ref="A1:D332"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -14431,6 +14462,27 @@
       <c r="D331" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:ZoneLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <f>IF(ISNA(VLOOKUP(B332,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>defect_depth</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J210"/>
+  <dimension ref="A1:J211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -7525,6 +7525,37 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211">
+        <f>IF(ISNA(VLOOKUP(B211,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>effective_radius</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Effective Radius</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>The as-built effective radius (or equivalent cross-sectional dimension) at a given depth, interpreted from a thermal integrity profiling temperature record by comparing the measured heat signature against the response expected for the design cross-section - a reduction indicates necking or a concrete deficiency, an increase indicates bulging. A result of diggs:ThermalIntegrityProfiling.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7540,7 +7571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D334"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -14483,6 +14514,48 @@
       <c r="D332" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <f>IF(ISNA(VLOOKUP(B333,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>effective_radius</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ThermalIntegrityProfiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <f>IF(ISNA(VLOOKUP(B334,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ThermalIntegrityProfiling</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -7556,6 +7556,37 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212">
+        <f>IF(ISNA(VLOOKUP(B212,AssociatedElements!B$2:B$1623,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>lateral_deflection</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Lateral Deflection</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Horizontal displacement of the load application point (or another stated gauge point) on a deep foundation element under a static lateral load test, measured against a stated datum. Distinct from properties.xml#settlement, which is explicitly vertical. A result of diggs:LateralLoadTest.</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7571,7 +7602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:D335"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -14556,6 +14587,27 @@
       <c r="D334" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:ThermalIntegrityProfiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <f>IF(ISNA(VLOOKUP(B335,Definitions!B$2:B$1623,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>lateral_deflection</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LateralLoadTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -7587,6 +7587,33 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>magnesium_content</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Magnesium Content</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Magnesium content by lab testing (corrosivity series). Completes the chemistry set the ground-aggressivity classifications are derived from: EN 206 grades chemical attack partly on magnesium ion content, and BS 8500 derives its ACEC class from sulfate AND magnesium together via BRE Special Digest 1, so an exposureClassification could be stated without the measurement that justifies it. Added at R10 from the Jazera project record (GBL-24136), which reports 571-954 ppm alongside its sulfate, chloride and pH results.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7602,7 +7629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D335"/>
+  <dimension ref="A1:D336"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -14608,6 +14635,23 @@
       <c r="D335" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LateralLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>magnesium_content</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
         </is>
       </c>
     </row>
